--- a/data/trans_camb/IP16A04-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16A04-Estudios-trans_camb.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,56</t>
+          <t>0,0; 12,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -641,22 +641,22 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,73; 0,0</t>
+          <t>-16,88; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-16,73; 0,0</t>
+          <t>-16,99; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 2,64</t>
+          <t>-5,13; 2,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 0,0</t>
+          <t>-8,38; 0,0</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 0,0</t>
+          <t>-5,92; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 5,65</t>
+          <t>-0,59; 5,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 0,98</t>
+          <t>-3,18; 0,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 2,83</t>
+          <t>-1,71; 2,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 0,26</t>
+          <t>-2,22; 0,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 3,57</t>
+          <t>-0,43; 3,59</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-62,42; —</t>
+          <t>-61,15; —</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-16,74; 0,0</t>
+          <t>-14,43; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,88; 3,87</t>
+          <t>-13,73; 3,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 5,4</t>
+          <t>-6,92; 5,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,58; 0,0</t>
+          <t>-11,27; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 1,61</t>
+          <t>-7,39; 2,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 0,98</t>
+          <t>-8,28; 0,97</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 0,34</t>
+          <t>-3,53; 0,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 3,95</t>
+          <t>-1,14; 3,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 1,26</t>
+          <t>-3,12; 1,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 1,32</t>
+          <t>-3,05; 1,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 0,43</t>
+          <t>-2,41; 0,46</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 2,0</t>
+          <t>-1,46; 1,94</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-73,66; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-92,42; 125,48</t>
+          <t>-92,21; 161,01</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-68,17; 386,8</t>
+          <t>-67,68; 385,67</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A04-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16A04-Estudios-trans_camb.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,52</t>
+          <t>0,0; 12,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -641,22 +641,22 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,88; 0,0</t>
+          <t>-16,26; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-16,99; 0,0</t>
+          <t>-16,24; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 2,61</t>
+          <t>-6,21; 2,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,38; 0,0</t>
+          <t>-8,86; 0,0</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 0,0</t>
+          <t>-3,96; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 5,66</t>
+          <t>-0,68; 5,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 0,98</t>
+          <t>-3,15; 0,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 2,98</t>
+          <t>-2,38; 2,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 0,25</t>
+          <t>-2,18; 0,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 3,59</t>
+          <t>-0,5; 3,75</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-61,15; —</t>
+          <t>-62,97; —</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-14,43; 0,0</t>
+          <t>-16,25; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,73; 3,84</t>
+          <t>-13,53; 3,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 5,65</t>
+          <t>-6,62; 5,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,27; 0,0</t>
+          <t>-11,44; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 2,05</t>
+          <t>-7,55; 2,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 0,97</t>
+          <t>-8,17; 0,99</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 0,34</t>
+          <t>-3,26; 0,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 3,85</t>
+          <t>-1,16; 4,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 1,04</t>
+          <t>-3,24; 1,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 1,32</t>
+          <t>-3,15; 1,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 0,46</t>
+          <t>-2,26; 0,5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 1,94</t>
+          <t>-1,25; 2,18</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-73,66; —</t>
+          <t>-72,99; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-92,21; 161,01</t>
+          <t>-91,73; 174,15</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-67,68; 385,67</t>
+          <t>-62,06; 641,99</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A04-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16A04-Estudios-trans_camb.xlsx
@@ -513,19 +513,19 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos laxantes</t>
+          <t>Menores que consumieron medicamentos laxantes</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-3,32</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-3,32</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>2,46</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-3,32</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-3,32</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,77</t>
+          <t>-16,73; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-16,73; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,26; 0,0</t>
+          <t>0,0; 13,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-16,24; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 2,62</t>
+          <t>-6,27; 2,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 0,0</t>
+          <t>-8,18; 0,0</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,3</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,61</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-0,83</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>2,29</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,3</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,61</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 0,0</t>
+          <t>-3,19; 0,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 5,73</t>
+          <t>-2,02; 2,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 0,99</t>
+          <t>-4,42; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 2,76</t>
+          <t>-0,66; 5,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 0,26</t>
+          <t>-2,47; 0,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 3,75</t>
+          <t>-0,53; 3,57</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-38,22%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>76,08%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>275,74%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-38,22%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>76,08%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-62,97; —</t>
+          <t>-62,42; —</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,49</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-2,31</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>-3,4</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>-1,47</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,49</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-2,31</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-16,25; 0,0</t>
+          <t>-6,9; 5,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,53; 3,85</t>
+          <t>-11,58; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 5,58</t>
+          <t>-16,74; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,44; 0,0</t>
+          <t>-12,88; 3,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 2,05</t>
+          <t>-7,22; 1,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 0,99</t>
+          <t>-8,29; 0,98</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>21,41%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>-43,35%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>21,41%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,55</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,6</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>-0,81</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>1,33</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,55</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,6</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 0,34</t>
+          <t>-3,17; 1,26</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 4,04</t>
+          <t>-3,2; 1,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 1,13</t>
+          <t>-3,47; 0,34</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 1,33</t>
+          <t>-1,12; 3,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 0,5</t>
+          <t>-2,4; 0,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 2,18</t>
+          <t>-1,15; 2,0</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-35,87%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-39,38%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>-70,73%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>116,23%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-35,87%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-39,38%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-72,99; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-91,73; 174,15</t>
+          <t>-92,42; 125,48</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-62,06; 641,99</t>
+          <t>-68,17; 386,8</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A04-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16A04-Estudios-trans_camb.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -118,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -131,6 +134,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -497,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -591,467 +600,269 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-3,32</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-3,32</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,46</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-0,29</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-1,59</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-0.7749847697808043</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.7749847697808043</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.6825533785089016</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-0.02532243953166382</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-0.3787211493539175</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-16,73; 0,0</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-16,73; 0,0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 13,56</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-6,27; 2,64</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-8,18; 0,0</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-4.527205451225677</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-4.558666304507108</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="n">
+        <v>-1.167893322144647</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-2.080032224803414</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-18,5%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>4.540746201489215</v>
+      </c>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="n">
+        <v>1.017151800766704</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="n">
+        <v>-0.06686301933457597</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-0,3</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,61</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,83</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,29</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-0,56</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,48</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr"/>
+      <c r="D8" s="6" t="inlineStr"/>
+      <c r="E8" s="6" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-3,19; 0,98</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-2,02; 2,83</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-4,42; 0,0</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-0,66; 5,65</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-2,47; 0,26</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-0,53; 3,57</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr"/>
+      <c r="D9" s="6" t="inlineStr"/>
+      <c r="E9" s="6" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n"/>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-38,22%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>76,08%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>275,74%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-68,73%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>182,44%</t>
-        </is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>-0.02358162882024821</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.1339049801115175</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.1608741080941266</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.5379568279547451</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-0.08899390207190178</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>0.3328449569548971</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-62,42; —</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-0.4619053587198032</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-0.2942417764788854</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-0.9322390062307579</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-0.05904031300157726</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-0.4251016267438765</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-0.02648362726079284</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0,49</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-2,31</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-3,4</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,47</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-1,34</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-1,77</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.2460448064826792</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.6824337602809866</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>1.314251229315288</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.06442125287596347</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>0.7861517475740699</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-6,9; 5,4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-11,58; 0,0</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-16,74; 0,0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-12,88; 3,87</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-7,22; 1,61</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-8,29; 0,98</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>-0.1611365323335053</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0.9149912553466192</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>3.343961525741541</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.5812245573648614</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>2.173830546512435</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>21,41%</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-43,35%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-49,13%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-64,7%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr"/>
+      <c r="D14" s="6" t="inlineStr"/>
+      <c r="E14" s="6" t="inlineStr"/>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="n">
+        <v>-0.4858818799572602</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr"/>
+      <c r="D15" s="6" t="inlineStr"/>
+      <c r="E15" s="6" t="inlineStr"/>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1059,153 +870,279 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-0,55</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-0,6</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,81</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,33</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,69</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,39</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>0.227428388463167</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.5141328224902592</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.4404747370503512</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-0.01926737718863777</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-0.1004552720471371</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>-0.27358325185522</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-3,17; 1,26</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-3,2; 1,32</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-3,47; 0,34</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-1,12; 3,95</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-2,4; 0,43</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-1,15; 2,0</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-1.538814189392769</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-2.562077380002923</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-2.217462571554454</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-1.361908899453546</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-1.044425129751827</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-1.204847446953824</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>-35,87%</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-39,38%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-70,73%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>116,23%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-51,0%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>28,86%</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1.492581380320701</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0.8557378779620829</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.6219372733133913</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>0.3703806087830305</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>-92,42; 125,48</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-68,17; 386,8</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>0.4423533735146348</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-0.04374229795257314</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.2112455397976689</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.5753131770987483</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr"/>
+      <c r="D20" s="6" t="inlineStr"/>
+      <c r="E20" s="6" t="inlineStr"/>
+      <c r="F20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr"/>
+      <c r="D21" s="6" t="inlineStr"/>
+      <c r="E21" s="6" t="inlineStr"/>
+      <c r="F21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-0.05303306156095567</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-0.1186333169665859</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-0.1226506791181488</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0.3609760028464648</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-0.08698123348661675</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>0.1144163703922565</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-0.5334564249036446</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-0.6326548345082822</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-0.5490953133844266</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-0.1484391765372677</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-0.4320894773535441</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-0.2196627669057621</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0.3321744355746113</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0.2610578194900589</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0.1750319497297274</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0.9134817817870504</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.1594416424330488</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>0.4596686743878325</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n"/>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>-0.1753032457062283</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-0.3921479337796599</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>-0.5816305196372072</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>1.711810008894471</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-0.3370902686328742</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>0.4434134063810271</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr"/>
+      <c r="D26" s="6" t="inlineStr"/>
+      <c r="E26" s="6" t="inlineStr"/>
+      <c r="F26" s="6" t="n">
+        <v>-0.7984497916900686</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.6325740458415322</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr"/>
+      <c r="D27" s="6" t="inlineStr"/>
+      <c r="E27" s="6" t="inlineStr"/>
+      <c r="F27" s="6" t="inlineStr"/>
+      <c r="G27" s="6" t="n">
+        <v>2.098156713972112</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>4.44509947742893</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1213,14 +1150,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A22:A27"/>
+    <mergeCell ref="A4:A9"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="A10:A15"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
